--- a/Run-Env/iManager/src/main/webapp/template/LogsStatsFile_service.xlsx
+++ b/Run-Env/iManager/src/main/webapp/template/LogsStatsFile_service.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ESB_workspace\workspace\Git\iGate_v5\Custom\iManager\src\main\webapp\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwonyongsu\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>평균 파일 크기 (kb)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>평균 처리 시간 (ms)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -73,7 +69,11 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>최대 파일 크기 (kb)</t>
+    <t>평균 파일 크기 (b)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 파일 크기 (b)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1236,13 +1236,13 @@
         <v>4</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>13</v>
